--- a/tevc实验记录.xlsx
+++ b/tevc实验记录.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\01-Joycecyq\2025-TEVC\TEVC-code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F43F2376-2F26-4847-865A-33FCB53006DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1712E413-1D27-47BB-9B87-ED57833DF72B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-6768" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10" yWindow="10" windowWidth="25580" windowHeight="13780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="80">
   <si>
     <t>v1</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -285,6 +285,66 @@
   </si>
   <si>
     <t>精简到最初破坏算子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V5/微调了原始算子/微调了reward/添加了e重置</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V2-60</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V5-10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">西北B区 / 858机 /20251121_141025 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">西北B区 / 858机 / 20251121_194609 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V5/每周期e重置0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V5/每2&amp;4周期e重置0.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西北B区 / 858机 / 20251121_205950</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西北B区 / 858机 / 20251122_100021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西北B区 / 875机 / 20251122_100750</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>未调整提前终止条件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>观察到best出现抖动</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西北B区 / 858机 / 20251122_113459</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修正抖动测试</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>西北B区 / 875机 / 20251122_113419</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -634,6 +694,72 @@
     <xf numFmtId="10" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -643,42 +769,6 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -687,42 +777,34 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="7" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -998,7 +1080,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O77"/>
+  <dimension ref="A1:O113"/>
   <sheetFormatPr defaultColWidth="8.9140625" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="38" style="34" customWidth="1"/>
@@ -1006,9 +1088,9 @@
     <col min="4" max="4" width="8.9140625" style="2"/>
     <col min="5" max="5" width="8.9140625" style="12"/>
     <col min="6" max="6" width="9.83203125" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" style="66" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" style="46" customWidth="1"/>
     <col min="8" max="8" width="8.9140625" style="2"/>
-    <col min="9" max="9" width="9.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.33203125" style="2" customWidth="1"/>
     <col min="10" max="11" width="8.9140625" style="2"/>
     <col min="12" max="12" width="15.25" style="2" customWidth="1"/>
     <col min="13" max="13" width="35.1640625" customWidth="1"/>
@@ -1017,22 +1099,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="42" x14ac:dyDescent="0.3">
-      <c r="A1" s="50" t="s">
+      <c r="A1" s="57" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="52" t="s">
+      <c r="B1" s="59" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="52" t="s">
+      <c r="C1" s="59" t="s">
         <v>27</v>
       </c>
-      <c r="D1" s="52" t="s">
+      <c r="D1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="52"/>
-      <c r="F1" s="52"/>
-      <c r="G1" s="52"/>
-      <c r="H1" s="54"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="61"/>
       <c r="I1" s="17" t="s">
         <v>31</v>
       </c>
@@ -1041,9 +1123,9 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="28.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="51"/>
-      <c r="B2" s="53"/>
-      <c r="C2" s="53"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="60"/>
+      <c r="C2" s="60"/>
       <c r="D2" s="31" t="s">
         <v>6</v>
       </c>
@@ -1053,7 +1135,7 @@
       <c r="F2" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="59" t="s">
+      <c r="G2" s="31" t="s">
         <v>3</v>
       </c>
       <c r="H2" s="33" t="s">
@@ -1066,28 +1148,28 @@
       <c r="D3" s="1"/>
       <c r="E3" s="30"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="60"/>
+      <c r="G3" s="42"/>
       <c r="H3" s="1"/>
       <c r="I3" s="17"/>
       <c r="J3"/>
     </row>
     <row r="4" spans="1:11" s="1" customFormat="1" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="53" t="s">
         <v>28</v>
       </c>
-      <c r="B4" s="55" t="s">
+      <c r="B4" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="55">
+      <c r="C4" s="62">
         <v>8</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="42"/>
-      <c r="F4" s="42"/>
-      <c r="G4" s="42"/>
-      <c r="H4" s="42"/>
+      <c r="E4" s="64"/>
+      <c r="F4" s="64"/>
+      <c r="G4" s="64"/>
+      <c r="H4" s="64"/>
       <c r="I4" s="1" t="s">
         <v>30</v>
       </c>
@@ -1099,9 +1181,9 @@
       </c>
     </row>
     <row r="5" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="45"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="55"/>
+      <c r="A5" s="53"/>
+      <c r="B5" s="62"/>
+      <c r="C5" s="62"/>
       <c r="D5" s="4" t="s">
         <v>14</v>
       </c>
@@ -1111,7 +1193,7 @@
       <c r="F5" s="5">
         <v>5333118</v>
       </c>
-      <c r="G5" s="61">
+      <c r="G5" s="43">
         <v>5127344</v>
       </c>
       <c r="H5" s="16">
@@ -1125,9 +1207,9 @@
       </c>
     </row>
     <row r="6" spans="1:11" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="45"/>
-      <c r="B6" s="55"/>
-      <c r="C6" s="55"/>
+      <c r="A6" s="53"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
       <c r="D6" s="4" t="s">
         <v>15</v>
       </c>
@@ -1137,7 +1219,7 @@
       <c r="F6" s="5">
         <v>6720412</v>
       </c>
-      <c r="G6" s="61">
+      <c r="G6" s="43">
         <v>6426080</v>
       </c>
       <c r="H6" s="16">
@@ -1151,9 +1233,9 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="45"/>
-      <c r="B7" s="55"/>
-      <c r="C7" s="55"/>
+      <c r="A7" s="53"/>
+      <c r="B7" s="62"/>
+      <c r="C7" s="62"/>
       <c r="D7" s="4" t="s">
         <v>7</v>
       </c>
@@ -1163,7 +1245,7 @@
       <c r="F7" s="4">
         <v>7534309</v>
       </c>
-      <c r="G7" s="62">
+      <c r="G7" s="13">
         <v>7227179</v>
       </c>
       <c r="H7" s="6">
@@ -1177,9 +1259,9 @@
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A8" s="45"/>
-      <c r="B8" s="55"/>
-      <c r="C8" s="55"/>
+      <c r="A8" s="53"/>
+      <c r="B8" s="62"/>
+      <c r="C8" s="62"/>
       <c r="D8" s="4" t="s">
         <v>8</v>
       </c>
@@ -1189,7 +1271,7 @@
       <c r="F8" s="4">
         <v>7770953</v>
       </c>
-      <c r="G8" s="63">
+      <c r="G8" s="41">
         <v>7451117</v>
       </c>
       <c r="H8" s="6">
@@ -1203,9 +1285,9 @@
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A9" s="45"/>
-      <c r="B9" s="55"/>
-      <c r="C9" s="55"/>
+      <c r="A9" s="53"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
       <c r="D9" s="4" t="s">
         <v>9</v>
       </c>
@@ -1215,7 +1297,7 @@
       <c r="F9" s="4">
         <v>7910588</v>
       </c>
-      <c r="G9" s="62">
+      <c r="G9" s="13">
         <v>7586978</v>
       </c>
       <c r="H9" s="6">
@@ -1226,9 +1308,9 @@
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="45"/>
-      <c r="B10" s="55"/>
-      <c r="C10" s="55"/>
+      <c r="A10" s="53"/>
+      <c r="B10" s="62"/>
+      <c r="C10" s="62"/>
       <c r="D10" s="4" t="s">
         <v>10</v>
       </c>
@@ -1238,7 +1320,7 @@
       <c r="F10" s="4">
         <v>7994545</v>
       </c>
-      <c r="G10" s="62">
+      <c r="G10" s="13">
         <v>7666741</v>
       </c>
       <c r="H10" s="6">
@@ -1249,9 +1331,9 @@
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="45"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
+      <c r="A11" s="53"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
       <c r="D11" s="4" t="s">
         <v>11</v>
       </c>
@@ -1261,7 +1343,7 @@
       <c r="F11" s="4">
         <v>10804813</v>
       </c>
-      <c r="G11" s="62">
+      <c r="G11" s="13">
         <v>10400370</v>
       </c>
       <c r="H11" s="6">
@@ -1278,9 +1360,9 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A12" s="45"/>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
+      <c r="A12" s="53"/>
+      <c r="B12" s="62"/>
+      <c r="C12" s="62"/>
       <c r="D12" s="4" t="s">
         <v>12</v>
       </c>
@@ -1290,7 +1372,7 @@
       <c r="F12" s="4">
         <v>13590647</v>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="13">
         <v>13067133</v>
       </c>
       <c r="H12" s="6">
@@ -1307,9 +1389,9 @@
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A13" s="45"/>
-      <c r="B13" s="55"/>
-      <c r="C13" s="55"/>
+      <c r="A13" s="53"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
       <c r="D13" s="4" t="s">
         <v>16</v>
       </c>
@@ -1319,7 +1401,7 @@
       <c r="F13" s="5">
         <v>14941329</v>
       </c>
-      <c r="G13" s="61">
+      <c r="G13" s="43">
         <v>14347380</v>
       </c>
       <c r="H13" s="16">
@@ -1330,9 +1412,9 @@
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A14" s="45"/>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
+      <c r="A14" s="53"/>
+      <c r="B14" s="62"/>
+      <c r="C14" s="62"/>
       <c r="D14" s="4" t="s">
         <v>17</v>
       </c>
@@ -1342,7 +1424,7 @@
       <c r="F14" s="5">
         <v>15407645</v>
       </c>
-      <c r="G14" s="61">
+      <c r="G14" s="43">
         <v>14793762</v>
       </c>
       <c r="H14" s="16">
@@ -1356,9 +1438,9 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A15" s="45"/>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
+      <c r="A15" s="53"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
       <c r="D15" s="4" t="s">
         <v>18</v>
       </c>
@@ -1368,7 +1450,7 @@
       <c r="F15" s="5">
         <v>15661542</v>
       </c>
-      <c r="G15" s="61">
+      <c r="G15" s="43">
         <v>15029237</v>
       </c>
       <c r="H15" s="16">
@@ -1379,9 +1461,9 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A16" s="45"/>
-      <c r="B16" s="55"/>
-      <c r="C16" s="55"/>
+      <c r="A16" s="53"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="62"/>
       <c r="D16" s="4" t="s">
         <v>19</v>
       </c>
@@ -1391,7 +1473,7 @@
       <c r="F16" s="5">
         <v>15636027</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G16" s="43">
         <v>15004943</v>
       </c>
       <c r="H16" s="16">
@@ -1402,22 +1484,22 @@
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A17" s="45" t="s">
+      <c r="A17" s="53" t="s">
         <v>29</v>
       </c>
-      <c r="B17" s="44" t="s">
+      <c r="B17" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="44">
+      <c r="C17" s="52">
         <v>8</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D17" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="E17" s="42"/>
-      <c r="F17" s="42"/>
-      <c r="G17" s="42"/>
-      <c r="H17" s="42"/>
+      <c r="E17" s="64"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="64"/>
+      <c r="H17" s="64"/>
       <c r="I17" s="1" t="s">
         <v>24</v>
       </c>
@@ -1429,9 +1511,9 @@
       </c>
     </row>
     <row r="18" spans="1:13" ht="14" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="45"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
       <c r="D18" s="4" t="s">
         <v>14</v>
       </c>
@@ -1441,7 +1523,7 @@
       <c r="F18" s="4">
         <v>5333092</v>
       </c>
-      <c r="G18" s="62">
+      <c r="G18" s="13">
         <v>5133902</v>
       </c>
       <c r="H18" s="6">
@@ -1455,9 +1537,9 @@
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A19" s="45"/>
-      <c r="B19" s="44"/>
-      <c r="C19" s="44"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
       <c r="D19" s="4" t="s">
         <v>15</v>
       </c>
@@ -1467,7 +1549,7 @@
       <c r="F19" s="4">
         <v>6713172</v>
       </c>
-      <c r="G19" s="62">
+      <c r="G19" s="13">
         <v>6421078</v>
       </c>
       <c r="H19" s="6">
@@ -1482,9 +1564,9 @@
       <c r="K19" s="1"/>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A20" s="45"/>
-      <c r="B20" s="44"/>
-      <c r="C20" s="44"/>
+      <c r="A20" s="53"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
       <c r="D20" s="4" t="s">
         <v>7</v>
       </c>
@@ -1494,7 +1576,7 @@
       <c r="F20" s="4">
         <v>7500013</v>
       </c>
-      <c r="G20" s="62">
+      <c r="G20" s="13">
         <v>7193892</v>
       </c>
       <c r="H20" s="6">
@@ -1508,9 +1590,9 @@
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A21" s="45"/>
-      <c r="B21" s="44"/>
-      <c r="C21" s="44"/>
+      <c r="A21" s="53"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
       <c r="D21" s="4" t="s">
         <v>8</v>
       </c>
@@ -1520,7 +1602,7 @@
       <c r="F21" s="4">
         <v>7738808</v>
       </c>
-      <c r="G21" s="62">
+      <c r="G21" s="13">
         <v>7418505</v>
       </c>
       <c r="H21" s="6">
@@ -1534,9 +1616,9 @@
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A22" s="45"/>
-      <c r="B22" s="44"/>
-      <c r="C22" s="44"/>
+      <c r="A22" s="53"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
       <c r="D22" s="4" t="s">
         <v>9</v>
       </c>
@@ -1546,7 +1628,7 @@
       <c r="F22" s="4">
         <v>7811960</v>
       </c>
-      <c r="G22" s="62">
+      <c r="G22" s="13">
         <v>7495921</v>
       </c>
       <c r="H22" s="6">
@@ -1557,9 +1639,9 @@
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A23" s="45"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="44"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
       <c r="D23" s="4" t="s">
         <v>10</v>
       </c>
@@ -1569,7 +1651,7 @@
       <c r="F23" s="4">
         <v>7837373</v>
       </c>
-      <c r="G23" s="62">
+      <c r="G23" s="13">
         <v>7525648</v>
       </c>
       <c r="H23" s="6">
@@ -1580,9 +1662,9 @@
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A24" s="45"/>
-      <c r="B24" s="44"/>
-      <c r="C24" s="44"/>
+      <c r="A24" s="53"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
       <c r="D24" s="4" t="s">
         <v>11</v>
       </c>
@@ -1592,7 +1674,7 @@
       <c r="F24" s="4">
         <v>10465211</v>
       </c>
-      <c r="G24" s="62">
+      <c r="G24" s="13">
         <v>10103151</v>
       </c>
       <c r="H24" s="6">
@@ -1609,9 +1691,9 @@
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A25" s="45"/>
-      <c r="B25" s="44"/>
-      <c r="C25" s="44"/>
+      <c r="A25" s="53"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
       <c r="D25" s="4" t="s">
         <v>12</v>
       </c>
@@ -1621,7 +1703,7 @@
       <c r="F25" s="4">
         <v>12978101</v>
       </c>
-      <c r="G25" s="62">
+      <c r="G25" s="13">
         <v>12478177</v>
       </c>
       <c r="H25" s="6">
@@ -1638,9 +1720,9 @@
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="44"/>
-      <c r="C26" s="44"/>
+      <c r="A26" s="53"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
       <c r="D26" s="4" t="s">
         <v>16</v>
       </c>
@@ -1650,7 +1732,7 @@
       <c r="F26" s="4">
         <v>14211224</v>
       </c>
-      <c r="G26" s="62">
+      <c r="G26" s="13">
         <v>13679695</v>
       </c>
       <c r="H26" s="6">
@@ -1664,9 +1746,9 @@
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A27" s="45"/>
-      <c r="B27" s="44"/>
-      <c r="C27" s="44"/>
+      <c r="A27" s="53"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
       <c r="D27" s="4" t="s">
         <v>17</v>
       </c>
@@ -1676,7 +1758,7 @@
       <c r="F27" s="4">
         <v>14898235</v>
       </c>
-      <c r="G27" s="62">
+      <c r="G27" s="13">
         <v>14348350</v>
       </c>
       <c r="H27" s="6">
@@ -1687,9 +1769,9 @@
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A28" s="45"/>
-      <c r="B28" s="44"/>
-      <c r="C28" s="44"/>
+      <c r="A28" s="53"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
       <c r="D28" s="4" t="s">
         <v>18</v>
       </c>
@@ -1699,7 +1781,7 @@
       <c r="F28" s="4">
         <v>14969889</v>
       </c>
-      <c r="G28" s="62">
+      <c r="G28" s="13">
         <v>14422992</v>
       </c>
       <c r="H28" s="6">
@@ -1710,9 +1792,9 @@
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A29" s="45"/>
-      <c r="B29" s="44"/>
-      <c r="C29" s="44"/>
+      <c r="A29" s="53"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
       <c r="D29" s="4" t="s">
         <v>19</v>
       </c>
@@ -1722,7 +1804,7 @@
       <c r="F29" s="4">
         <v>15247843</v>
       </c>
-      <c r="G29" s="62">
+      <c r="G29" s="13">
         <v>14687457</v>
       </c>
       <c r="H29" s="6">
@@ -1733,22 +1815,22 @@
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="53" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="55" t="s">
+      <c r="B31" s="62" t="s">
         <v>21</v>
       </c>
-      <c r="C31" s="55">
+      <c r="C31" s="62">
         <v>8</v>
       </c>
-      <c r="D31" s="43" t="s">
+      <c r="D31" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
+      <c r="E31" s="65"/>
+      <c r="F31" s="65"/>
+      <c r="G31" s="65"/>
+      <c r="H31" s="65"/>
       <c r="I31" s="1" t="s">
         <v>30</v>
       </c>
@@ -1764,9 +1846,9 @@
       <c r="M31" s="2"/>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A32" s="45"/>
-      <c r="B32" s="55"/>
-      <c r="C32" s="55"/>
+      <c r="A32" s="53"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
       <c r="D32" s="4" t="s">
         <v>14</v>
       </c>
@@ -1776,7 +1858,7 @@
       <c r="F32" s="5">
         <v>5334791</v>
       </c>
-      <c r="G32" s="64">
+      <c r="G32" s="44">
         <v>5131177</v>
       </c>
       <c r="H32" s="16">
@@ -1788,9 +1870,9 @@
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A33" s="45"/>
-      <c r="B33" s="55"/>
-      <c r="C33" s="55"/>
+      <c r="A33" s="53"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="62"/>
       <c r="D33" s="4" t="s">
         <v>34</v>
       </c>
@@ -1800,7 +1882,7 @@
       <c r="F33" s="5">
         <v>5334731</v>
       </c>
-      <c r="G33" s="64">
+      <c r="G33" s="44">
         <v>5140370</v>
       </c>
       <c r="H33" s="16">
@@ -1821,9 +1903,9 @@
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A34" s="45"/>
-      <c r="B34" s="55"/>
-      <c r="C34" s="55"/>
+      <c r="A34" s="53"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
       <c r="D34" s="4" t="s">
         <v>15</v>
       </c>
@@ -1831,7 +1913,7 @@
       <c r="F34" s="4">
         <v>6721502</v>
       </c>
-      <c r="G34" s="65">
+      <c r="G34" s="45">
         <v>6432551</v>
       </c>
       <c r="H34" s="6">
@@ -1850,9 +1932,9 @@
       <c r="M34" s="2"/>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A35" s="45"/>
-      <c r="B35" s="55"/>
-      <c r="C35" s="55"/>
+      <c r="A35" s="53"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
       <c r="D35" s="4" t="s">
         <v>38</v>
       </c>
@@ -1860,7 +1942,7 @@
       <c r="F35" s="4">
         <v>7540757</v>
       </c>
-      <c r="G35" s="63">
+      <c r="G35" s="41">
         <v>7226388</v>
       </c>
       <c r="H35" s="6">
@@ -1878,9 +1960,9 @@
       <c r="M35" s="2"/>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A36" s="45"/>
-      <c r="B36" s="55"/>
-      <c r="C36" s="55"/>
+      <c r="A36" s="53"/>
+      <c r="B36" s="62"/>
+      <c r="C36" s="62"/>
       <c r="D36" s="19" t="s">
         <v>8</v>
       </c>
@@ -1888,7 +1970,7 @@
       <c r="F36" s="19">
         <v>7768781</v>
       </c>
-      <c r="G36" s="65">
+      <c r="G36" s="45">
         <v>7452607</v>
       </c>
       <c r="H36" s="21">
@@ -1908,9 +1990,9 @@
       </c>
     </row>
     <row r="37" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A37" s="45"/>
-      <c r="B37" s="55"/>
-      <c r="C37" s="55"/>
+      <c r="A37" s="53"/>
+      <c r="B37" s="62"/>
+      <c r="C37" s="62"/>
       <c r="D37" s="4" t="s">
         <v>9</v>
       </c>
@@ -1918,7 +2000,7 @@
       <c r="F37" s="4">
         <v>7912540</v>
       </c>
-      <c r="G37" s="65">
+      <c r="G37" s="45">
         <v>7589504</v>
       </c>
       <c r="H37" s="6">
@@ -1935,9 +2017,9 @@
       </c>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A38" s="45"/>
-      <c r="B38" s="55"/>
-      <c r="C38" s="55"/>
+      <c r="A38" s="53"/>
+      <c r="B38" s="62"/>
+      <c r="C38" s="62"/>
       <c r="D38" s="4" t="s">
         <v>10</v>
       </c>
@@ -1945,7 +2027,7 @@
       <c r="F38" s="4">
         <v>7994824</v>
       </c>
-      <c r="G38" s="65">
+      <c r="G38" s="45">
         <v>7671143</v>
       </c>
       <c r="H38" s="6">
@@ -1959,9 +2041,9 @@
       </c>
     </row>
     <row r="39" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A39" s="45"/>
-      <c r="B39" s="55"/>
-      <c r="C39" s="55"/>
+      <c r="A39" s="53"/>
+      <c r="B39" s="62"/>
+      <c r="C39" s="62"/>
       <c r="D39" s="4" t="s">
         <v>11</v>
       </c>
@@ -1969,7 +2051,7 @@
       <c r="F39" s="4">
         <v>10806147</v>
       </c>
-      <c r="G39" s="65">
+      <c r="G39" s="45">
         <v>10408528</v>
       </c>
       <c r="H39" s="6">
@@ -1989,9 +2071,9 @@
       </c>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A40" s="45"/>
-      <c r="B40" s="55"/>
-      <c r="C40" s="55"/>
+      <c r="A40" s="53"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
       <c r="D40" s="4" t="s">
         <v>12</v>
       </c>
@@ -1999,7 +2081,7 @@
       <c r="F40" s="5">
         <v>13648215</v>
       </c>
-      <c r="G40" s="64">
+      <c r="G40" s="44">
         <v>13108865</v>
       </c>
       <c r="H40" s="16">
@@ -2019,9 +2101,9 @@
       </c>
     </row>
     <row r="41" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A41" s="45"/>
-      <c r="B41" s="55"/>
-      <c r="C41" s="55"/>
+      <c r="A41" s="53"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="62"/>
       <c r="D41" s="4" t="s">
         <v>16</v>
       </c>
@@ -2029,7 +2111,7 @@
       <c r="F41" s="5">
         <v>14909654</v>
       </c>
-      <c r="G41" s="61">
+      <c r="G41" s="43">
         <v>14320999</v>
       </c>
       <c r="H41" s="16">
@@ -2043,9 +2125,9 @@
       </c>
     </row>
     <row r="42" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A42" s="45"/>
-      <c r="B42" s="55"/>
-      <c r="C42" s="55"/>
+      <c r="A42" s="53"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="62"/>
       <c r="D42" s="4" t="s">
         <v>17</v>
       </c>
@@ -2053,7 +2135,7 @@
       <c r="F42" s="5">
         <v>15450067</v>
       </c>
-      <c r="G42" s="64">
+      <c r="G42" s="44">
         <v>14825037</v>
       </c>
       <c r="H42" s="16">
@@ -2070,9 +2152,9 @@
       </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A43" s="45"/>
-      <c r="B43" s="55"/>
-      <c r="C43" s="55"/>
+      <c r="A43" s="53"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="62"/>
       <c r="D43" s="4" t="s">
         <v>18</v>
       </c>
@@ -2080,7 +2162,7 @@
       <c r="F43" s="5">
         <v>15655094</v>
       </c>
-      <c r="G43" s="61">
+      <c r="G43" s="43">
         <v>15025711</v>
       </c>
       <c r="H43" s="16">
@@ -2094,15 +2176,15 @@
       </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A44" s="45"/>
-      <c r="B44" s="55"/>
-      <c r="C44" s="55"/>
+      <c r="A44" s="53"/>
+      <c r="B44" s="62"/>
+      <c r="C44" s="62"/>
       <c r="D44" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E44" s="10"/>
       <c r="F44" s="5"/>
-      <c r="G44" s="61"/>
+      <c r="G44" s="43"/>
       <c r="H44" s="16"/>
       <c r="I44" s="3">
         <v>15165752</v>
@@ -2112,30 +2194,30 @@
       </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A46" s="45" t="s">
+      <c r="A46" s="53" t="s">
         <v>43</v>
       </c>
-      <c r="B46" s="44" t="s">
+      <c r="B46" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C46" s="44">
+      <c r="C46" s="52">
         <v>8</v>
       </c>
-      <c r="D46" s="48" t="s">
+      <c r="D46" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="E46" s="48"/>
-      <c r="F46" s="48"/>
-      <c r="G46" s="48"/>
-      <c r="H46" s="48"/>
+      <c r="E46" s="56"/>
+      <c r="F46" s="56"/>
+      <c r="G46" s="56"/>
+      <c r="H46" s="56"/>
       <c r="I46" s="1"/>
       <c r="J46" s="1"/>
       <c r="K46" s="1"/>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A47" s="45"/>
-      <c r="B47" s="44"/>
-      <c r="C47" s="44"/>
+      <c r="A47" s="53"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="52"/>
       <c r="D47" s="4" t="s">
         <v>14</v>
       </c>
@@ -2143,19 +2225,19 @@
       <c r="F47" s="4">
         <v>5324762</v>
       </c>
-      <c r="G47" s="62">
+      <c r="G47" s="13">
         <v>5123959</v>
       </c>
       <c r="H47" s="6"/>
       <c r="J47" s="1"/>
-      <c r="M47" s="46" t="s">
+      <c r="M47" s="54" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A48" s="45"/>
-      <c r="B48" s="44"/>
-      <c r="C48" s="44"/>
+      <c r="A48" s="53"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
       <c r="D48" s="4" t="s">
         <v>15</v>
       </c>
@@ -2163,7 +2245,7 @@
       <c r="F48" s="4">
         <v>6690908</v>
       </c>
-      <c r="G48" s="62">
+      <c r="G48" s="13">
         <v>6399437</v>
       </c>
       <c r="H48" s="6">
@@ -2171,12 +2253,12 @@
       </c>
       <c r="J48" s="1"/>
       <c r="K48" s="1"/>
-      <c r="M48" s="47"/>
+      <c r="M48" s="55"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A49" s="45"/>
-      <c r="B49" s="44"/>
-      <c r="C49" s="44"/>
+      <c r="A49" s="53"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
       <c r="D49" s="4" t="s">
         <v>7</v>
       </c>
@@ -2186,18 +2268,18 @@
       <c r="F49" s="4">
         <v>7465859</v>
       </c>
-      <c r="G49" s="62">
+      <c r="G49" s="13">
         <v>7156081</v>
       </c>
       <c r="H49" s="6">
         <v>-4.1500000000000002E-2</v>
       </c>
-      <c r="M49" s="47"/>
+      <c r="M49" s="55"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A50" s="45"/>
-      <c r="B50" s="44"/>
-      <c r="C50" s="44"/>
+      <c r="A50" s="53"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="52"/>
       <c r="D50" s="4" t="s">
         <v>8</v>
       </c>
@@ -2205,18 +2287,18 @@
       <c r="F50" s="4">
         <v>7724583</v>
       </c>
-      <c r="G50" s="62">
+      <c r="G50" s="13">
         <v>7408875</v>
       </c>
       <c r="H50" s="6">
         <v>-4.0899999999999999E-2</v>
       </c>
-      <c r="M50" s="47"/>
+      <c r="M50" s="55"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A51" s="45"/>
-      <c r="B51" s="44"/>
-      <c r="C51" s="44"/>
+      <c r="A51" s="53"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="52"/>
       <c r="D51" s="25" t="s">
         <v>9</v>
       </c>
@@ -2224,7 +2306,7 @@
       <c r="F51" s="25">
         <v>7797742</v>
       </c>
-      <c r="G51" s="62">
+      <c r="G51" s="13">
         <v>7481245</v>
       </c>
       <c r="H51" s="28"/>
@@ -2232,12 +2314,12 @@
       <c r="J51" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="M51" s="47"/>
+      <c r="M51" s="55"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A52" s="45"/>
-      <c r="B52" s="44"/>
-      <c r="C52" s="44"/>
+      <c r="A52" s="53"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
       <c r="D52" s="4" t="s">
         <v>10</v>
       </c>
@@ -2245,18 +2327,18 @@
       <c r="F52" s="4">
         <v>7854467</v>
       </c>
-      <c r="G52" s="62">
+      <c r="G52" s="13">
         <v>7546413</v>
       </c>
       <c r="H52" s="6">
         <v>-3.9199999999999999E-2</v>
       </c>
-      <c r="M52" s="47"/>
+      <c r="M52" s="55"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A53" s="45"/>
-      <c r="B53" s="44"/>
-      <c r="C53" s="44"/>
+      <c r="A53" s="53"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
       <c r="D53" s="4" t="s">
         <v>11</v>
       </c>
@@ -2264,104 +2346,104 @@
       <c r="F53" s="4">
         <v>10419715</v>
       </c>
-      <c r="G53" s="62">
+      <c r="G53" s="13">
         <v>10054576</v>
       </c>
       <c r="H53" s="6">
         <v>-3.5000000000000003E-2</v>
       </c>
-      <c r="M53" s="47"/>
+      <c r="M53" s="55"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A54" s="45"/>
-      <c r="B54" s="44"/>
-      <c r="C54" s="44"/>
+      <c r="A54" s="53"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="52"/>
       <c r="D54" s="4" t="s">
         <v>12</v>
       </c>
       <c r="E54" s="11"/>
       <c r="F54" s="4"/>
-      <c r="G54" s="62"/>
+      <c r="G54" s="13"/>
       <c r="H54" s="6"/>
-      <c r="M54" s="47"/>
+      <c r="M54" s="55"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A55" s="45"/>
-      <c r="B55" s="44"/>
-      <c r="C55" s="44"/>
+      <c r="A55" s="53"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="52"/>
       <c r="D55" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E55" s="11"/>
       <c r="F55" s="4"/>
-      <c r="G55" s="62"/>
+      <c r="G55" s="13"/>
       <c r="H55" s="6"/>
-      <c r="M55" s="47"/>
+      <c r="M55" s="55"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A56" s="45"/>
-      <c r="B56" s="44"/>
-      <c r="C56" s="44"/>
+      <c r="A56" s="53"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="52"/>
       <c r="D56" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E56" s="11"/>
       <c r="F56" s="4"/>
-      <c r="G56" s="62"/>
+      <c r="G56" s="13"/>
       <c r="H56" s="6"/>
-      <c r="M56" s="47"/>
+      <c r="M56" s="55"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A57" s="45"/>
-      <c r="B57" s="44"/>
-      <c r="C57" s="44"/>
+      <c r="A57" s="53"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="52"/>
       <c r="D57" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="4"/>
-      <c r="G57" s="62"/>
+      <c r="G57" s="13"/>
       <c r="H57" s="6"/>
-      <c r="M57" s="47"/>
+      <c r="M57" s="55"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A58" s="45"/>
-      <c r="B58" s="44"/>
-      <c r="C58" s="44"/>
+      <c r="A58" s="53"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
       <c r="D58" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E58" s="11"/>
       <c r="F58" s="4"/>
-      <c r="G58" s="62"/>
+      <c r="G58" s="13"/>
       <c r="H58" s="6"/>
-      <c r="M58" s="47"/>
+      <c r="M58" s="55"/>
     </row>
     <row r="59" spans="1:14" ht="42" x14ac:dyDescent="0.3">
-      <c r="A59" s="45" t="s">
+      <c r="A59" s="53" t="s">
         <v>47</v>
       </c>
-      <c r="B59" s="44" t="s">
+      <c r="B59" s="52" t="s">
         <v>42</v>
       </c>
-      <c r="C59" s="44">
+      <c r="C59" s="52">
         <v>8</v>
       </c>
-      <c r="D59" s="49" t="s">
+      <c r="D59" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="E59" s="49"/>
-      <c r="F59" s="49"/>
-      <c r="G59" s="49"/>
-      <c r="H59" s="49"/>
+      <c r="E59" s="50"/>
+      <c r="F59" s="50"/>
+      <c r="G59" s="50"/>
+      <c r="H59" s="50"/>
       <c r="I59" s="1" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A60" s="45"/>
-      <c r="B60" s="44"/>
-      <c r="C60" s="44"/>
+      <c r="A60" s="53"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
       <c r="D60" s="4" t="s">
         <v>14</v>
       </c>
@@ -2371,7 +2453,7 @@
       <c r="F60" s="4">
         <v>5334817</v>
       </c>
-      <c r="G60" s="62">
+      <c r="G60" s="13">
         <v>5126019</v>
       </c>
       <c r="H60" s="6">
@@ -2379,9 +2461,9 @@
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="A61" s="45"/>
-      <c r="B61" s="44"/>
-      <c r="C61" s="44"/>
+      <c r="A61" s="53"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="52"/>
       <c r="D61" s="4" t="s">
         <v>11</v>
       </c>
@@ -2391,7 +2473,7 @@
       <c r="F61" s="4">
         <v>10764653</v>
       </c>
-      <c r="G61" s="62">
+      <c r="G61" s="13">
         <v>10365215</v>
       </c>
       <c r="H61" s="6">
@@ -2399,19 +2481,19 @@
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.3">
-      <c r="B62" s="44" t="s">
+      <c r="B62" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="C62" s="44">
+      <c r="C62" s="52">
         <v>8</v>
       </c>
-      <c r="D62" s="49" t="s">
+      <c r="D62" s="50" t="s">
         <v>53</v>
       </c>
-      <c r="E62" s="49"/>
-      <c r="F62" s="49"/>
-      <c r="G62" s="49"/>
-      <c r="H62" s="49"/>
+      <c r="E62" s="50"/>
+      <c r="F62" s="50"/>
+      <c r="G62" s="50"/>
+      <c r="H62" s="50"/>
       <c r="I62" s="2" t="s">
         <v>61</v>
       </c>
@@ -2420,8 +2502,8 @@
       <c r="A63" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B63" s="44"/>
-      <c r="C63" s="44"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
       <c r="D63" s="4" t="s">
         <v>14</v>
       </c>
@@ -2431,7 +2513,7 @@
       <c r="F63" s="4">
         <v>5330521</v>
       </c>
-      <c r="G63" s="62">
+      <c r="G63" s="13">
         <v>5124921</v>
       </c>
       <c r="H63" s="6">
@@ -2445,8 +2527,8 @@
       <c r="A64" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="B64" s="44"/>
-      <c r="C64" s="44"/>
+      <c r="B64" s="52"/>
+      <c r="C64" s="52"/>
       <c r="D64" s="4" t="s">
         <v>34</v>
       </c>
@@ -2456,7 +2538,7 @@
       <c r="F64" s="4">
         <v>5322405</v>
       </c>
-      <c r="G64" s="62">
+      <c r="G64" s="13">
         <v>5125427</v>
       </c>
       <c r="H64" s="6">
@@ -2482,7 +2564,7 @@
       <c r="C65" s="2">
         <v>8</v>
       </c>
-      <c r="D65" s="67" t="s">
+      <c r="D65" s="47" t="s">
         <v>34</v>
       </c>
       <c r="E65" s="38">
@@ -2491,7 +2573,7 @@
       <c r="F65" s="39">
         <v>5335843</v>
       </c>
-      <c r="G65" s="66">
+      <c r="G65" s="46">
         <v>5136599</v>
       </c>
       <c r="H65" s="40">
@@ -2505,13 +2587,13 @@
       </c>
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A66" s="68" t="s">
+      <c r="A66" s="51" t="s">
         <v>63</v>
       </c>
-      <c r="B66" s="44" t="s">
+      <c r="B66" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="C66" s="44">
+      <c r="C66" s="52">
         <v>8</v>
       </c>
       <c r="D66" s="4" t="s">
@@ -2523,7 +2605,7 @@
       <c r="F66" s="4">
         <v>5333836</v>
       </c>
-      <c r="G66" s="62">
+      <c r="G66" s="13">
         <v>5129095</v>
       </c>
       <c r="H66" s="6">
@@ -2540,9 +2622,9 @@
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="68"/>
-      <c r="B67" s="44"/>
-      <c r="C67" s="44"/>
+      <c r="A67" s="51"/>
+      <c r="B67" s="52"/>
+      <c r="C67" s="52"/>
       <c r="D67" s="4" t="s">
         <v>15</v>
       </c>
@@ -2552,7 +2634,7 @@
       <c r="F67" s="4">
         <v>6713704</v>
       </c>
-      <c r="G67" s="62">
+      <c r="G67" s="13">
         <v>6422334</v>
       </c>
       <c r="H67" s="6">
@@ -2564,9 +2646,9 @@
       <c r="O67" s="37"/>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A68" s="68"/>
-      <c r="B68" s="44"/>
-      <c r="C68" s="44"/>
+      <c r="A68" s="51"/>
+      <c r="B68" s="52"/>
+      <c r="C68" s="52"/>
       <c r="D68" s="4" t="s">
         <v>38</v>
       </c>
@@ -2576,7 +2658,7 @@
       <c r="F68" s="4">
         <v>7534426</v>
       </c>
-      <c r="G68" s="62">
+      <c r="G68" s="13">
         <v>7225556</v>
       </c>
       <c r="H68" s="6">
@@ -2584,9 +2666,9 @@
       </c>
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A69" s="68"/>
-      <c r="B69" s="44"/>
-      <c r="C69" s="44"/>
+      <c r="A69" s="51"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="52"/>
       <c r="D69" s="4" t="s">
         <v>8</v>
       </c>
@@ -2596,7 +2678,7 @@
       <c r="F69" s="4">
         <v>7767009</v>
       </c>
-      <c r="G69" s="62">
+      <c r="G69" s="13">
         <v>7449362</v>
       </c>
       <c r="H69" s="6">
@@ -2607,9 +2689,9 @@
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="68"/>
-      <c r="B70" s="44"/>
-      <c r="C70" s="44"/>
+      <c r="A70" s="51"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="52"/>
       <c r="D70" s="4" t="s">
         <v>9</v>
       </c>
@@ -2619,7 +2701,7 @@
       <c r="F70" s="4">
         <v>7904437</v>
       </c>
-      <c r="G70" s="62">
+      <c r="G70" s="13">
         <v>7581319</v>
       </c>
       <c r="H70" s="6">
@@ -2627,21 +2709,21 @@
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A71" s="68"/>
-      <c r="B71" s="44"/>
-      <c r="C71" s="44"/>
+      <c r="A71" s="51"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
       <c r="D71" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E71" s="11"/>
       <c r="F71" s="4"/>
-      <c r="G71" s="62"/>
+      <c r="G71" s="13"/>
       <c r="H71" s="4"/>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A72" s="68"/>
-      <c r="B72" s="44"/>
-      <c r="C72" s="44"/>
+      <c r="A72" s="51"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="52"/>
       <c r="D72" s="4" t="s">
         <v>11</v>
       </c>
@@ -2649,7 +2731,7 @@
       <c r="F72" s="4">
         <v>10714011</v>
       </c>
-      <c r="G72" s="62">
+      <c r="G72" s="13">
         <v>10303478</v>
       </c>
       <c r="H72" s="6">
@@ -2657,9 +2739,9 @@
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A73" s="68"/>
-      <c r="B73" s="44"/>
-      <c r="C73" s="44"/>
+      <c r="A73" s="51"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="52"/>
       <c r="D73" s="4" t="s">
         <v>12</v>
       </c>
@@ -2669,7 +2751,7 @@
       <c r="F73" s="4">
         <v>13581294</v>
       </c>
-      <c r="G73" s="62">
+      <c r="G73" s="13">
         <v>13042871</v>
       </c>
       <c r="H73" s="6">
@@ -2677,9 +2759,9 @@
       </c>
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" s="68"/>
-      <c r="B74" s="44"/>
-      <c r="C74" s="44"/>
+      <c r="A74" s="51"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
       <c r="D74" s="4" t="s">
         <v>16</v>
       </c>
@@ -2689,7 +2771,7 @@
       <c r="F74" s="4">
         <v>14883833</v>
       </c>
-      <c r="G74" s="62">
+      <c r="G74" s="13">
         <v>14293707</v>
       </c>
       <c r="H74" s="6">
@@ -2697,9 +2779,9 @@
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A75" s="68"/>
-      <c r="B75" s="44"/>
-      <c r="C75" s="44"/>
+      <c r="A75" s="51"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
       <c r="D75" s="4" t="s">
         <v>17</v>
       </c>
@@ -2709,7 +2791,7 @@
       <c r="F75" s="4">
         <v>15395151</v>
       </c>
-      <c r="G75" s="62">
+      <c r="G75" s="13">
         <v>14780155</v>
       </c>
       <c r="H75" s="6">
@@ -2717,111 +2799,707 @@
       </c>
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" s="68"/>
-      <c r="B76" s="44"/>
-      <c r="C76" s="44"/>
+      <c r="A76" s="51"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
       <c r="D76" s="4" t="s">
         <v>18</v>
       </c>
       <c r="E76" s="11"/>
       <c r="F76" s="4"/>
-      <c r="G76" s="62"/>
+      <c r="G76" s="13"/>
       <c r="H76" s="4"/>
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A77" s="68"/>
-      <c r="B77" s="44"/>
-      <c r="C77" s="44"/>
+      <c r="A77" s="51"/>
+      <c r="B77" s="52"/>
+      <c r="C77" s="52"/>
       <c r="D77" s="4" t="s">
         <v>19</v>
       </c>
       <c r="E77" s="11"/>
       <c r="F77" s="4"/>
-      <c r="G77" s="62"/>
+      <c r="G77" s="13"/>
       <c r="H77" s="4"/>
     </row>
+    <row r="80" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="B80" s="4"/>
+      <c r="C80" s="4"/>
+      <c r="D80" s="50" t="s">
+        <v>65</v>
+      </c>
+      <c r="E80" s="50"/>
+      <c r="F80" s="50"/>
+      <c r="G80" s="50"/>
+      <c r="H80" s="50"/>
+      <c r="J80" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81" s="51" t="s">
+        <v>68</v>
+      </c>
+      <c r="B81" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="C81" s="52">
+        <v>8</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E81" s="11">
+        <v>790.02</v>
+      </c>
+      <c r="F81" s="4">
+        <v>5332852</v>
+      </c>
+      <c r="G81" s="13">
+        <v>5131153</v>
+      </c>
+      <c r="H81" s="6">
+        <v>-3.78E-2</v>
+      </c>
+      <c r="I81" s="2">
+        <v>2</v>
+      </c>
+      <c r="J81" s="2">
+        <v>5127173</v>
+      </c>
+      <c r="K81" s="13"/>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="51"/>
+      <c r="B82" s="52"/>
+      <c r="C82" s="52"/>
+      <c r="D82" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E82" s="11">
+        <v>807.05</v>
+      </c>
+      <c r="F82" s="4">
+        <v>6712875</v>
+      </c>
+      <c r="G82" s="13">
+        <v>6419162</v>
+      </c>
+      <c r="H82" s="6">
+        <v>-4.3799999999999999E-2</v>
+      </c>
+      <c r="J82" s="2">
+        <v>6403274</v>
+      </c>
+      <c r="K82" s="13"/>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83" s="51"/>
+      <c r="B83" s="52"/>
+      <c r="C83" s="52"/>
+      <c r="D83" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E83" s="11">
+        <v>760.76</v>
+      </c>
+      <c r="F83" s="4">
+        <v>7512067</v>
+      </c>
+      <c r="G83" s="13">
+        <v>7202153</v>
+      </c>
+      <c r="H83" s="6">
+        <v>-4.1300000000000003E-2</v>
+      </c>
+      <c r="I83" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="J83" s="2">
+        <v>7182817</v>
+      </c>
+      <c r="K83" s="13"/>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" s="51"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="52"/>
+      <c r="D84" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="11">
+        <v>789.07</v>
+      </c>
+      <c r="F84" s="4">
+        <v>7702223</v>
+      </c>
+      <c r="G84" s="13">
+        <v>7383615</v>
+      </c>
+      <c r="H84" s="6">
+        <v>-4.1399999999999999E-2</v>
+      </c>
+      <c r="I84" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="J84" s="3">
+        <v>7405840</v>
+      </c>
+      <c r="K84" s="13"/>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85" s="51"/>
+      <c r="B85" s="52"/>
+      <c r="C85" s="52"/>
+      <c r="D85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E85" s="11">
+        <v>887.23</v>
+      </c>
+      <c r="F85" s="4">
+        <v>7865161</v>
+      </c>
+      <c r="G85" s="13">
+        <v>7543172</v>
+      </c>
+      <c r="H85" s="6">
+        <v>-4.0899999999999999E-2</v>
+      </c>
+      <c r="I85" s="2">
+        <v>1</v>
+      </c>
+      <c r="J85" s="14">
+        <v>7572108</v>
+      </c>
+      <c r="K85" s="13"/>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" s="51"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
+      <c r="D86" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E86" s="11">
+        <v>810.85</v>
+      </c>
+      <c r="F86" s="4">
+        <v>7891659</v>
+      </c>
+      <c r="G86" s="13">
+        <v>7571191</v>
+      </c>
+      <c r="H86" s="6">
+        <v>-4.0599999999999997E-2</v>
+      </c>
+      <c r="I86" s="2">
+        <v>1</v>
+      </c>
+      <c r="J86" s="3">
+        <v>7589888</v>
+      </c>
+      <c r="K86" s="13"/>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87" s="51"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
+      <c r="D87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="11">
+        <v>920.77</v>
+      </c>
+      <c r="F87" s="4">
+        <v>10624916</v>
+      </c>
+      <c r="G87" s="13">
+        <v>10234370</v>
+      </c>
+      <c r="H87" s="6">
+        <v>-3.6799999999999999E-2</v>
+      </c>
+      <c r="I87" s="2">
+        <v>2</v>
+      </c>
+      <c r="J87" s="2">
+        <v>10010708</v>
+      </c>
+      <c r="K87" s="13"/>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" s="51"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
+      <c r="D88" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" s="11">
+        <v>997.58</v>
+      </c>
+      <c r="F88" s="4">
+        <v>13115099</v>
+      </c>
+      <c r="G88" s="13">
+        <v>12600660</v>
+      </c>
+      <c r="H88" s="6">
+        <v>-3.9199999999999999E-2</v>
+      </c>
+      <c r="I88" s="2">
+        <v>1</v>
+      </c>
+      <c r="J88" s="3">
+        <v>12624667</v>
+      </c>
+      <c r="K88" s="13"/>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89" s="51"/>
+      <c r="B89" s="52"/>
+      <c r="C89" s="52"/>
+      <c r="D89" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E89" s="11">
+        <v>1166.43</v>
+      </c>
+      <c r="F89" s="4">
+        <v>14268766</v>
+      </c>
+      <c r="G89" s="13">
+        <v>13725567</v>
+      </c>
+      <c r="H89" s="6">
+        <v>-3.8100000000000002E-2</v>
+      </c>
+      <c r="I89" s="2">
+        <v>1</v>
+      </c>
+      <c r="J89" s="3">
+        <v>13835256</v>
+      </c>
+      <c r="K89" s="13"/>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90" s="51"/>
+      <c r="B90" s="52"/>
+      <c r="C90" s="52"/>
+      <c r="D90" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="11">
+        <v>1350.9</v>
+      </c>
+      <c r="F90" s="4">
+        <v>15042713</v>
+      </c>
+      <c r="G90" s="13">
+        <v>14456663</v>
+      </c>
+      <c r="H90" s="6">
+        <v>-3.9E-2</v>
+      </c>
+      <c r="I90" s="2">
+        <v>1</v>
+      </c>
+      <c r="J90" s="2">
+        <v>14329778</v>
+      </c>
+      <c r="K90" s="13"/>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91" s="51"/>
+      <c r="B91" s="52"/>
+      <c r="C91" s="52"/>
+      <c r="D91" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E91" s="11">
+        <v>1117.4100000000001</v>
+      </c>
+      <c r="F91" s="4">
+        <v>14940559</v>
+      </c>
+      <c r="G91" s="13">
+        <v>14412948</v>
+      </c>
+      <c r="H91" s="49">
+        <v>-3.5299999999999998E-2</v>
+      </c>
+      <c r="I91" s="2">
+        <v>1</v>
+      </c>
+      <c r="J91" s="3">
+        <v>14565104</v>
+      </c>
+      <c r="K91" s="13"/>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92" s="51"/>
+      <c r="B92" s="52"/>
+      <c r="C92" s="52"/>
+      <c r="D92" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E92" s="11">
+        <v>1463.46</v>
+      </c>
+      <c r="F92" s="4">
+        <v>15289672</v>
+      </c>
+      <c r="G92" s="13">
+        <v>14734373</v>
+      </c>
+      <c r="H92" s="6">
+        <v>-3.6299999999999999E-2</v>
+      </c>
+      <c r="I92" s="2">
+        <v>1</v>
+      </c>
+      <c r="J92" s="2">
+        <v>14731415</v>
+      </c>
+      <c r="K92" s="13"/>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93" s="48"/>
+      <c r="B93" s="4"/>
+      <c r="C93" s="4"/>
+      <c r="D93" s="4"/>
+      <c r="E93" s="11"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="6"/>
+      <c r="K93" s="46"/>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94" s="48"/>
+      <c r="B94" s="4"/>
+      <c r="C94" s="4"/>
+      <c r="D94" s="50" t="s">
+        <v>70</v>
+      </c>
+      <c r="E94" s="50"/>
+      <c r="F94" s="50"/>
+      <c r="G94" s="50"/>
+      <c r="H94" s="50"/>
+      <c r="K94" s="46"/>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C95" s="4">
+        <v>8</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E95" s="11">
+        <v>3692.1</v>
+      </c>
+      <c r="F95" s="4">
+        <v>5335251</v>
+      </c>
+      <c r="G95" s="13">
+        <v>5133350</v>
+      </c>
+      <c r="H95" s="6">
+        <v>-3.78E-2</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D96" s="50" t="s">
+        <v>71</v>
+      </c>
+      <c r="E96" s="50"/>
+      <c r="F96" s="50"/>
+      <c r="G96" s="50"/>
+      <c r="H96" s="50"/>
+    </row>
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A97" s="34" t="s">
+        <v>72</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C97" s="4">
+        <v>8</v>
+      </c>
+      <c r="D97" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E97" s="12">
+        <v>3701.78</v>
+      </c>
+      <c r="F97" s="2">
+        <v>5336862</v>
+      </c>
+      <c r="G97" s="46">
+        <v>5132081</v>
+      </c>
+      <c r="H97" s="49">
+        <v>-3.8399999999999997E-2</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A98" s="34" t="s">
+        <v>74</v>
+      </c>
+      <c r="B98" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C98" s="4">
+        <v>6</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E98" s="12">
+        <v>3840.13</v>
+      </c>
+      <c r="F98" s="2">
+        <v>5337503</v>
+      </c>
+      <c r="G98" s="46">
+        <v>5150532</v>
+      </c>
+      <c r="H98" s="49">
+        <v>-3.5000000000000003E-2</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A99" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C99" s="4">
+        <v>6</v>
+      </c>
+      <c r="D99" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A102" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="B102" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C102" s="4">
+        <v>8</v>
+      </c>
+      <c r="D102" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E102" s="12">
+        <v>3831.57</v>
+      </c>
+      <c r="F102" s="2">
+        <v>5338568</v>
+      </c>
+      <c r="G102" s="46">
+        <v>5140115</v>
+      </c>
+      <c r="H102" s="49">
+        <v>-3.7199999999999997E-2</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A103" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="B103" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C103" s="4">
+        <v>8</v>
+      </c>
+      <c r="D103" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D104" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D105" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D106" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D107" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D108" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D109" s="4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D110" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D111" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D112" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="4:4" x14ac:dyDescent="0.3">
+      <c r="D113" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A66:A77"/>
-    <mergeCell ref="B66:B77"/>
+  <mergeCells count="37">
     <mergeCell ref="C66:C77"/>
     <mergeCell ref="B62:B64"/>
     <mergeCell ref="C62:C64"/>
-    <mergeCell ref="D62:H62"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:H1"/>
     <mergeCell ref="B4:B16"/>
     <mergeCell ref="A4:A16"/>
-    <mergeCell ref="A31:A44"/>
-    <mergeCell ref="B31:B44"/>
-    <mergeCell ref="C31:C44"/>
     <mergeCell ref="C4:C16"/>
     <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D59:H59"/>
-    <mergeCell ref="A59:A61"/>
     <mergeCell ref="M47:M58"/>
     <mergeCell ref="D46:H46"/>
     <mergeCell ref="A46:A58"/>
     <mergeCell ref="B46:B58"/>
     <mergeCell ref="C46:C58"/>
-    <mergeCell ref="D17:H17"/>
-    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="D96:H96"/>
     <mergeCell ref="B59:B61"/>
     <mergeCell ref="C59:C61"/>
     <mergeCell ref="A17:A29"/>
     <mergeCell ref="B17:B29"/>
     <mergeCell ref="C17:C29"/>
+    <mergeCell ref="D62:H62"/>
+    <mergeCell ref="A31:A44"/>
+    <mergeCell ref="B31:B44"/>
+    <mergeCell ref="C31:C44"/>
+    <mergeCell ref="D59:H59"/>
+    <mergeCell ref="A59:A61"/>
+    <mergeCell ref="D17:H17"/>
+    <mergeCell ref="D31:H31"/>
+    <mergeCell ref="A66:A77"/>
+    <mergeCell ref="B66:B77"/>
+    <mergeCell ref="D80:H80"/>
+    <mergeCell ref="A81:A92"/>
+    <mergeCell ref="B81:B92"/>
+    <mergeCell ref="C81:C92"/>
+    <mergeCell ref="D94:H94"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <conditionalFormatting sqref="A1:A1048576">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="858机">
+      <formula>NOT(ISERROR(SEARCH("858机",A1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="875机">
+      <formula>NOT(ISERROR(SEARCH("875机",A1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E7374FE-3622-4BD7-AC24-07A35CEC5BC6}">
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AI13"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="16" max="30" width="0" hidden="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+    <row r="1" spans="1:35" x14ac:dyDescent="0.3">
+      <c r="A1" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="57"/>
-      <c r="C1" s="57"/>
-      <c r="D1" s="57"/>
-      <c r="E1" s="57"/>
-      <c r="F1" s="56" t="s">
+      <c r="B1" s="67"/>
+      <c r="C1" s="67"/>
+      <c r="D1" s="67"/>
+      <c r="E1" s="67"/>
+      <c r="F1" s="66" t="s">
         <v>59</v>
       </c>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
-      <c r="J1" s="57"/>
-      <c r="K1" s="43" t="s">
-        <v>33</v>
-      </c>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="58" t="s">
+      <c r="G1" s="67"/>
+      <c r="H1" s="67"/>
+      <c r="I1" s="67"/>
+      <c r="J1" s="67"/>
+      <c r="K1" s="65" t="s">
+        <v>66</v>
+      </c>
+      <c r="L1" s="65"/>
+      <c r="M1" s="65"/>
+      <c r="N1" s="65"/>
+      <c r="O1" s="65"/>
+      <c r="P1" s="68" t="s">
         <v>44</v>
       </c>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="44" t="s">
+      <c r="Q1" s="68"/>
+      <c r="R1" s="68"/>
+      <c r="S1" s="68"/>
+      <c r="T1" s="68"/>
+      <c r="U1" s="52" t="s">
         <v>41</v>
       </c>
-      <c r="V1" s="44"/>
-      <c r="W1" s="44"/>
-      <c r="X1" s="44"/>
-      <c r="Y1" s="44"/>
-    </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="V1" s="52"/>
+      <c r="W1" s="52"/>
+      <c r="X1" s="52"/>
+      <c r="Y1" s="52"/>
+      <c r="Z1" s="50" t="s">
+        <v>53</v>
+      </c>
+      <c r="AA1" s="50"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
+      <c r="AD1" s="50"/>
+      <c r="AE1" s="50" t="s">
+        <v>67</v>
+      </c>
+      <c r="AF1" s="50"/>
+      <c r="AG1" s="50"/>
+      <c r="AH1" s="50"/>
+      <c r="AI1" s="50"/>
+    </row>
+    <row r="2" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>14</v>
       </c>
@@ -2896,14 +3574,29 @@
       <c r="AB2" s="4">
         <v>5333836</v>
       </c>
-      <c r="AC2" s="62">
+      <c r="AC2" s="13">
         <v>5129095</v>
       </c>
       <c r="AD2" s="6">
         <v>-3.8399999999999997E-2</v>
       </c>
-    </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE2" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF2" s="11">
+        <v>790.02</v>
+      </c>
+      <c r="AG2" s="4">
+        <v>5332852</v>
+      </c>
+      <c r="AH2" s="13">
+        <v>5131153</v>
+      </c>
+      <c r="AI2" s="6">
+        <v>-3.78E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>15</v>
       </c>
@@ -2963,14 +3656,29 @@
       <c r="AB3" s="4">
         <v>6713704</v>
       </c>
-      <c r="AC3" s="62">
+      <c r="AC3" s="13">
         <v>6422334</v>
       </c>
       <c r="AD3" s="6">
         <v>-4.3400000000000001E-2</v>
       </c>
-    </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF3" s="11">
+        <v>807.05</v>
+      </c>
+      <c r="AG3" s="4">
+        <v>6712875</v>
+      </c>
+      <c r="AH3" s="13">
+        <v>6419162</v>
+      </c>
+      <c r="AI3" s="6">
+        <v>-4.3799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>7</v>
       </c>
@@ -3032,14 +3740,29 @@
       <c r="AB4" s="4">
         <v>7534426</v>
       </c>
-      <c r="AC4" s="62">
+      <c r="AC4" s="13">
         <v>7225556</v>
       </c>
       <c r="AD4" s="6">
         <v>-4.1000000000000002E-2</v>
       </c>
-    </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="AF4" s="11">
+        <v>760.76</v>
+      </c>
+      <c r="AG4" s="4">
+        <v>7512067</v>
+      </c>
+      <c r="AH4" s="13">
+        <v>7202153</v>
+      </c>
+      <c r="AI4" s="6">
+        <v>-4.1300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>8</v>
       </c>
@@ -3099,14 +3822,29 @@
       <c r="AB5" s="4">
         <v>7767009</v>
       </c>
-      <c r="AC5" s="62">
+      <c r="AC5" s="13">
         <v>7449362</v>
       </c>
       <c r="AD5" s="6">
         <v>-4.0899999999999999E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE5" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF5" s="11">
+        <v>789.07</v>
+      </c>
+      <c r="AG5" s="4">
+        <v>7702223</v>
+      </c>
+      <c r="AH5" s="13">
+        <v>7383615</v>
+      </c>
+      <c r="AI5" s="6">
+        <v>-4.1399999999999999E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -3164,14 +3902,29 @@
       <c r="AB6" s="4">
         <v>7904437</v>
       </c>
-      <c r="AC6" s="62">
+      <c r="AC6" s="13">
         <v>7581319</v>
       </c>
       <c r="AD6" s="6">
         <v>-4.0899999999999999E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AF6" s="11">
+        <v>887.23</v>
+      </c>
+      <c r="AG6" s="4">
+        <v>7865161</v>
+      </c>
+      <c r="AH6" s="13">
+        <v>7543172</v>
+      </c>
+      <c r="AI6" s="6">
+        <v>-4.0899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -3227,10 +3980,25 @@
       </c>
       <c r="AA7" s="11"/>
       <c r="AB7" s="4"/>
-      <c r="AC7" s="62"/>
+      <c r="AC7" s="13"/>
       <c r="AD7" s="4"/>
-    </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE7" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="AF7" s="11">
+        <v>810.85</v>
+      </c>
+      <c r="AG7" s="4">
+        <v>7891659</v>
+      </c>
+      <c r="AH7" s="13">
+        <v>7571191</v>
+      </c>
+      <c r="AI7" s="6">
+        <v>-4.0599999999999997E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A8" s="4" t="s">
         <v>11</v>
       </c>
@@ -3303,14 +4071,29 @@
       <c r="AB8" s="4">
         <v>10714011</v>
       </c>
-      <c r="AC8" s="62">
+      <c r="AC8" s="13">
         <v>10303478</v>
       </c>
       <c r="AD8" s="6">
         <v>-3.8300000000000001E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF8" s="11">
+        <v>920.77</v>
+      </c>
+      <c r="AG8" s="4">
+        <v>10624916</v>
+      </c>
+      <c r="AH8" s="13">
+        <v>10234370</v>
+      </c>
+      <c r="AI8" s="6">
+        <v>-3.6799999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
@@ -3364,14 +4147,29 @@
       <c r="AB9" s="4">
         <v>13581294</v>
       </c>
-      <c r="AC9" s="62">
+      <c r="AC9" s="13">
         <v>13042871</v>
       </c>
       <c r="AD9" s="6">
         <v>-3.9600000000000003E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE9" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF9" s="11">
+        <v>997.58</v>
+      </c>
+      <c r="AG9" s="4">
+        <v>13115099</v>
+      </c>
+      <c r="AH9" s="13">
+        <v>12600660</v>
+      </c>
+      <c r="AI9" s="6">
+        <v>-3.9199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>16</v>
       </c>
@@ -3425,14 +4223,29 @@
       <c r="AB10" s="4">
         <v>14883833</v>
       </c>
-      <c r="AC10" s="62">
+      <c r="AC10" s="13">
         <v>14293707</v>
       </c>
       <c r="AD10" s="6">
         <v>-3.9600000000000003E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE10" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="AF10" s="11">
+        <v>1166.43</v>
+      </c>
+      <c r="AG10" s="4">
+        <v>14268766</v>
+      </c>
+      <c r="AH10" s="13">
+        <v>13725567</v>
+      </c>
+      <c r="AI10" s="6">
+        <v>-3.8100000000000002E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>17</v>
       </c>
@@ -3486,14 +4299,29 @@
       <c r="AB11" s="4">
         <v>15395151</v>
       </c>
-      <c r="AC11" s="62">
+      <c r="AC11" s="13">
         <v>14780155</v>
       </c>
       <c r="AD11" s="6">
         <v>-3.9899999999999998E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE11" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="AF11" s="11">
+        <v>1350.9</v>
+      </c>
+      <c r="AG11" s="4">
+        <v>15042713</v>
+      </c>
+      <c r="AH11" s="13">
+        <v>14456663</v>
+      </c>
+      <c r="AI11" s="6">
+        <v>-3.9E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>18</v>
       </c>
@@ -3543,10 +4371,25 @@
       </c>
       <c r="AA12" s="11"/>
       <c r="AB12" s="4"/>
-      <c r="AC12" s="62"/>
+      <c r="AC12" s="13"/>
       <c r="AD12" s="4"/>
-    </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.3">
+      <c r="AE12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="AF12" s="11">
+        <v>1117.4100000000001</v>
+      </c>
+      <c r="AG12" s="4">
+        <v>14940559</v>
+      </c>
+      <c r="AH12" s="13">
+        <v>14412948</v>
+      </c>
+      <c r="AI12" s="49">
+        <v>-3.5299999999999998E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>19</v>
       </c>
@@ -3590,11 +4433,28 @@
       </c>
       <c r="AA13" s="11"/>
       <c r="AB13" s="4"/>
-      <c r="AC13" s="62"/>
+      <c r="AC13" s="13"/>
       <c r="AD13" s="4"/>
+      <c r="AE13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="AF13" s="11">
+        <v>1463.46</v>
+      </c>
+      <c r="AG13" s="4">
+        <v>15289672</v>
+      </c>
+      <c r="AH13" s="13">
+        <v>14734373</v>
+      </c>
+      <c r="AI13" s="6">
+        <v>-3.6299999999999999E-2</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="7">
+    <mergeCell ref="AE1:AI1"/>
+    <mergeCell ref="Z1:AD1"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="F1:J1"/>
     <mergeCell ref="K1:O1"/>
